--- a/public/openpos.xlsx
+++ b/public/openpos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nishant\shopify-backend\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80E00F16-72CC-402B-B534-E6A10A470057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B696249-37A0-414A-B07D-F8376817E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -626,16 +626,16 @@
         <v>0</v>
       </c>
       <c r="J2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="6">
-        <v>1518.4</v>
+        <v>0</v>
       </c>
       <c r="L2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="6">
-        <v>1188.8399999999999</v>
+        <v>0</v>
       </c>
       <c r="N2" s="6">
         <v>0</v>
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="T2" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" s="6">
-        <v>76.8</v>
+        <v>0</v>
       </c>
       <c r="V2" s="6">
         <v>3</v>
@@ -724,31 +724,31 @@
         <v>3</v>
       </c>
       <c r="Q3" s="6">
-        <v>15355</v>
+        <v>14472</v>
       </c>
       <c r="R3" s="6">
         <v>4</v>
       </c>
       <c r="S3" s="6">
-        <v>27170</v>
+        <v>8347.6</v>
       </c>
       <c r="T3" s="6">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="U3" s="6">
-        <v>82580.66</v>
+        <v>34876.94</v>
       </c>
       <c r="V3" s="6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="W3" s="6">
-        <v>148106.51999999999</v>
+        <v>109730.08</v>
       </c>
       <c r="X3" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="6">
-        <v>124240.26</v>
+        <v>125641.1</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -822,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="X4" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" s="6">
-        <v>18128.72</v>
+        <v>15169.2</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="O5" s="6">
-        <v>1654.8</v>
+        <v>399</v>
       </c>
       <c r="P5" s="6">
         <v>0</v>
@@ -887,22 +887,22 @@
         <v>0</v>
       </c>
       <c r="T5" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" s="6">
-        <v>3150</v>
+        <v>0</v>
       </c>
       <c r="V5" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="W5" s="6">
-        <v>31095.279999999999</v>
+        <v>8790</v>
       </c>
       <c r="X5" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="6">
-        <v>11791.2</v>
+        <v>5201.2</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -976,10 +976,10 @@
         <v>85469.46</v>
       </c>
       <c r="X6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y6" s="6">
-        <v>79753.600000000006</v>
+        <v>183983.6</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1124,16 +1124,16 @@
         <v>0</v>
       </c>
       <c r="V8" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="W8" s="6">
-        <v>164295.21</v>
+        <v>20630.61</v>
       </c>
       <c r="X8" s="6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y8" s="6">
-        <v>259950.94</v>
+        <v>255274.92</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="T9" s="6">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U9" s="6">
-        <v>38847.35</v>
+        <v>35322.5</v>
       </c>
       <c r="V9" s="6">
         <v>12</v>
@@ -1207,10 +1207,10 @@
         <v>287544.31</v>
       </c>
       <c r="X9" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y9" s="6">
-        <v>80280.5</v>
+        <v>52601.7</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="P10" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="6">
-        <v>6069.6</v>
+        <v>6109.55</v>
       </c>
       <c r="R10" s="6">
         <v>5</v>
@@ -1272,16 +1272,16 @@
         <v>40692.25</v>
       </c>
       <c r="T10" s="6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U10" s="6">
-        <v>119594.8</v>
+        <v>57503.3</v>
       </c>
       <c r="V10" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W10" s="6">
-        <v>169311.05</v>
+        <v>155562.54999999999</v>
       </c>
       <c r="X10" s="6">
         <v>27</v>
@@ -1491,34 +1491,34 @@
         <v>0</v>
       </c>
       <c r="P13" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="6">
-        <v>23503.06</v>
+        <v>14028</v>
       </c>
       <c r="R13" s="6">
+        <v>4</v>
+      </c>
+      <c r="S13" s="6">
+        <v>18335.2</v>
+      </c>
+      <c r="T13" s="6">
+        <v>10</v>
+      </c>
+      <c r="U13" s="6">
+        <v>111322.96</v>
+      </c>
+      <c r="V13" s="6">
         <v>14</v>
       </c>
-      <c r="S13" s="6">
-        <v>58213.1</v>
-      </c>
-      <c r="T13" s="6">
-        <v>14</v>
-      </c>
-      <c r="U13" s="6">
-        <v>194405.36</v>
-      </c>
-      <c r="V13" s="6">
-        <v>18</v>
-      </c>
       <c r="W13" s="6">
-        <v>322180.78000000003</v>
+        <v>265670.13</v>
       </c>
       <c r="X13" s="6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y13" s="6">
-        <v>246896.71</v>
+        <v>229744.01</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1574,28 +1574,28 @@
         <v>0</v>
       </c>
       <c r="R14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="6">
-        <v>2470</v>
+        <v>0</v>
       </c>
       <c r="T14" s="6">
+        <v>6</v>
+      </c>
+      <c r="U14" s="6">
+        <v>8932.35</v>
+      </c>
+      <c r="V14" s="6">
+        <v>9</v>
+      </c>
+      <c r="W14" s="6">
+        <v>26141.96</v>
+      </c>
+      <c r="X14" s="6">
         <v>11</v>
       </c>
-      <c r="U14" s="6">
-        <v>31656.91</v>
-      </c>
-      <c r="V14" s="6">
-        <v>14</v>
-      </c>
-      <c r="W14" s="6">
-        <v>40294.04</v>
-      </c>
-      <c r="X14" s="6">
-        <v>15</v>
-      </c>
       <c r="Y14" s="6">
-        <v>72896.160000000003</v>
+        <v>39341.160000000003</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -1660,7 +1660,7 @@
         <v>2</v>
       </c>
       <c r="U15" s="6">
-        <v>96331</v>
+        <v>77438.5</v>
       </c>
       <c r="V15" s="6">
         <v>2</v>
@@ -1669,10 +1669,10 @@
         <v>12590</v>
       </c>
       <c r="X15" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15" s="6">
-        <v>4506.99</v>
+        <v>6290.97</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
@@ -1828,10 +1828,10 @@
         <v>0</v>
       </c>
       <c r="P18" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6">
-        <v>11662</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6">
         <v>1</v>
@@ -1846,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="V18" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W18" s="6">
-        <v>29984.59</v>
+        <v>21392.59</v>
       </c>
       <c r="X18" s="6">
         <v>1</v>
@@ -1964,52 +1964,52 @@
         <v>4010</v>
       </c>
       <c r="J20" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="6">
-        <v>27317.98</v>
+        <v>25799.58</v>
       </c>
       <c r="L20" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M20" s="6">
-        <v>4043.44</v>
+        <v>2854.6000000000004</v>
       </c>
       <c r="N20" s="6">
         <v>1</v>
       </c>
       <c r="O20" s="6">
-        <v>1654.8</v>
+        <v>399</v>
       </c>
       <c r="P20" s="6">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="6">
-        <v>61752.46</v>
+        <v>39772.35</v>
       </c>
       <c r="R20" s="6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="S20" s="6">
-        <v>223320.05</v>
+        <v>162149.75</v>
       </c>
       <c r="T20" s="6">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="U20" s="6">
-        <v>608904.23</v>
+        <v>367657.9</v>
       </c>
       <c r="V20" s="6">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="W20" s="6">
-        <v>1413587.87</v>
+        <v>1116238.32</v>
       </c>
       <c r="X20" s="6">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="Y20" s="6">
-        <v>1207549.6700000002</v>
+        <v>1222352.4500000002</v>
       </c>
     </row>
   </sheetData>
